--- a/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Hogares con problemas de temperatura en la vivienda (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,38; 72,5</t>
+          <t>44,51; 74,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,2; 61,21</t>
+          <t>39,5; 62,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,27; 64,11</t>
+          <t>44,5; 65,05</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,54; 55,87</t>
+          <t>40,64; 56,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,92; 42,75</t>
+          <t>34,19; 42,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,27; 47,7</t>
+          <t>38,5; 47,61</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,08; 35,38</t>
+          <t>22,98; 35,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,36; 38,8</t>
+          <t>25,56; 38,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,65; 35,55</t>
+          <t>26,06; 35,58</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,14; 51,32</t>
+          <t>38,82; 51,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,01; 40,85</t>
+          <t>34,07; 40,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 44,42</t>
+          <t>37,31; 43,96</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas de temperatura en la vivienda (tasa de respuesta: 99,97%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32256</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>31374</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>63630</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24336; 40714</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>24493; 38614</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>51924; 75900</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>211052</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>198052</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>409104</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187156; 258169</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>176626; 219096</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>376222; 465231</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43256</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>57363</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100619</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34143; 53014</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>46622; 70923</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>86242; 117751</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>286563</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>286789</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>573352</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>257662; 343061</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>259269; 310694</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>531536; 626339</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,51; 74,46</t>
+          <t>43,32; 73,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,5; 62,28</t>
+          <t>39,04; 62,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,5; 65,05</t>
+          <t>44,37; 63,21</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,64; 56,06</t>
+          <t>40,78; 56,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,19; 42,41</t>
+          <t>33,82; 42,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,5; 47,61</t>
+          <t>38,59; 48,2</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,98; 35,69</t>
+          <t>23,3; 35,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,56; 38,88</t>
+          <t>25,28; 38,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,06; 35,58</t>
+          <t>25,99; 35,16</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 51,69</t>
+          <t>38,54; 50,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,07; 40,83</t>
+          <t>34,25; 41,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,31; 43,96</t>
+          <t>37,5; 44,11</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24336; 40714</t>
+          <t>23684; 40284</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24493; 38614</t>
+          <t>24208; 38690</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51924; 75900</t>
+          <t>51777; 73758</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187156; 258169</t>
+          <t>187790; 260602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>176626; 219096</t>
+          <t>174721; 219375</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>376222; 465231</t>
+          <t>377097; 470952</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34143; 53014</t>
+          <t>34616; 52771</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46622; 70923</t>
+          <t>46111; 70307</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86242; 117751</t>
+          <t>86011; 116363</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257662; 343061</t>
+          <t>255816; 337523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>259269; 310694</t>
+          <t>260623; 312103</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>531536; 626339</t>
+          <t>534249; 628480</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,32; 73,68</t>
+          <t>41,02; 63,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,04; 62,4</t>
+          <t>39,0; 64,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,37; 63,21</t>
+          <t>42,95; 60,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,78; 56,59</t>
+          <t>35,57; 44,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,82; 42,46</t>
+          <t>39,64; 47,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,59; 48,2</t>
+          <t>38,45; 44,62</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,3; 35,52</t>
+          <t>24,4; 36,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,28; 38,54</t>
+          <t>22,45; 35,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,99; 35,16</t>
+          <t>25,34; 34,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,54; 50,85</t>
+          <t>34,75; 41,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,25; 41,01</t>
+          <t>37,32; 44,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,5; 44,11</t>
+          <t>37,21; 42,06</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1383,27 +1383,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63630</t>
+          <t>53987</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23684; 40284</t>
+          <t>23271; 35900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24208; 38690</t>
+          <t>18233; 29987</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51777; 73758</t>
+          <t>44454; 62458</t>
         </is>
       </c>
     </row>
@@ -1591,27 +1591,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>271</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211052</t>
+          <t>189721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>198052</t>
+          <t>188302</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>409104</t>
+          <t>378024</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187790; 260602</t>
+          <t>169216; 211098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174721; 219375</t>
+          <t>171423; 206001</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>377097; 470952</t>
+          <t>349216; 405183</t>
         </is>
       </c>
     </row>
@@ -1799,27 +1799,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>50443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57363</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100619</t>
+          <t>93280</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34616; 52771</t>
+          <t>40858; 61918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46111; 70307</t>
+          <t>33421; 52186</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86011; 116363</t>
+          <t>80178; 109331</t>
         </is>
       </c>
     </row>
@@ -2007,27 +2007,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>368</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286563</t>
+          <t>270003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>286789</t>
+          <t>255287</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>573352</t>
+          <t>525290</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>255816; 337523</t>
+          <t>243222; 292631</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>260623; 312103</t>
+          <t>234411; 276460</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>534249; 628480</t>
+          <t>494173; 558557</t>
         </is>
       </c>
     </row>
